--- a/AAII_Financials/Yearly/LVMUY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LVMUY_YR_FIN.xlsx
@@ -2222,10 +2222,10 @@
         <v>5548900</v>
       </c>
       <c r="E42" s="3">
-        <v>4118400</v>
+        <v>4119500</v>
       </c>
       <c r="F42" s="3">
-        <v>3884200</v>
+        <v>3883100</v>
       </c>
       <c r="G42" s="3">
         <v>3830300</v>
@@ -2375,10 +2375,10 @@
         <v>4446400</v>
       </c>
       <c r="E45" s="3">
-        <v>598400</v>
+        <v>597400</v>
       </c>
       <c r="F45" s="3">
-        <v>934000</v>
+        <v>935100</v>
       </c>
       <c r="G45" s="3">
         <v>869900</v>
@@ -4471,25 +4471,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-4515700</v>
+        <v>-5362200</v>
       </c>
       <c r="E91" s="3">
-        <v>-4881500</v>
+        <v>-5726300</v>
       </c>
       <c r="F91" s="3">
-        <v>-7524000</v>
+        <v>-8265700</v>
       </c>
       <c r="G91" s="3">
-        <v>-4699200</v>
+        <v>-5310500</v>
       </c>
       <c r="H91" s="3">
-        <v>-3042200</v>
+        <v>-3029700</v>
       </c>
       <c r="I91" s="3">
-        <v>-2425700</v>
+        <v>-3031200</v>
       </c>
       <c r="J91" s="3">
-        <v>-3209500</v>
+        <v>-3696600</v>
       </c>
       <c r="K91" s="3">
         <v>-2965400</v>
